--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="115">
   <si>
     <t>Property</t>
   </si>
@@ -338,6 +338,9 @@
     <t>Ratio.numerator</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationQuantity}
 </t>
   </si>
@@ -345,26 +348,26 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>薬剤に関する数量と単位を定めたデータイプ</t>
-  </si>
-  <si>
-    <t>薬剤に関する数量と単位を定めている。ValueおよびCodeを必須としている。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>.numerator</t>
   </si>
   <si>
     <t>Ratio.denominator</t>
   </si>
   <si>
     <t>パッケージ量</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
 </sst>
 </file>
@@ -707,7 +710,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="45.1875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1173,20 +1176,18 @@
         <v>76</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N5" t="s" s="2">
         <v>108</v>
       </c>
+      <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>76</v>
@@ -1244,24 +1245,24 @@
         <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AL5" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="AL5" t="s" s="2">
-        <v>111</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1281,20 +1282,18 @@
         <v>76</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M6" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M6" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N6" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
         <v>76</v>
@@ -1343,7 +1342,7 @@
         <v>76</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>77</v>
@@ -1352,16 +1351,16 @@
         <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>109</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -674,43 +674,43 @@
   <dimension ref="A1:AL6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="18.125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="18.125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="15.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="15.5390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.0078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.1875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationratio-amount.xlsx
@@ -266,8 +266,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-rat-1:Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.exists() and denominator.exists()) or (numerator.empty() and denominator.empty() and extension.exists())}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+rat-1:分子と分母の両方が存在するか、両方が存在します。両方が欠席している場合、いくつかの拡張が存在するものとします / Numerator and denominator SHALL both be present, or both are absent. If both are absent, there SHALL be some extension present {(numerator.exists() and denominator.exists()) or (numerator.empty() and denominator.empty() and extension.exists())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -286,10 +286,10 @@
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -309,13 +309,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -331,8 +331,8 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Ratio.numerator</t>
@@ -348,10 +348,10 @@
     <t>投与量</t>
   </si>
   <si>
-    <t>The value of the numerator.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>分子の値。 / The value of the numerator.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -364,7 +364,7 @@
     <t>パッケージ量</t>
   </si>
   <si>
-    <t>The value of the denominator.</t>
+    <t>分母の値。 / The value of the denominator.</t>
   </si>
   <si>
     <t>.denominator</t>
